--- a/data/trans_orig/PCS12_SP_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91008</t>
+          <t>91246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127915</t>
+          <t>129428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112880</t>
+          <t>115759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151403</t>
+          <t>151828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216313</t>
+          <t>211240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270587</t>
+          <t>270100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366149</t>
+          <t>364636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403056</t>
+          <t>402818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>316086</t>
+          <t>315661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354609</t>
+          <t>351730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690966</t>
+          <t>691453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745240</t>
+          <t>750313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149794</t>
+          <t>152162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198180</t>
+          <t>200650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222243</t>
+          <t>221239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270346</t>
+          <t>270853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387240</t>
+          <t>388090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>457872</t>
+          <t>456999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>537309</t>
+          <t>534839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585695</t>
+          <t>583327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355148</t>
+          <t>354641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403251</t>
+          <t>404255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903110</t>
+          <t>903983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973742</t>
+          <t>972892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194395</t>
+          <t>193646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241717</t>
+          <t>240804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307577</t>
+          <t>307675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359807</t>
+          <t>360907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>511825</t>
+          <t>518760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589669</t>
+          <t>589699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396951</t>
+          <t>397864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>444273</t>
+          <t>445022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329937</t>
+          <t>328837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382167</t>
+          <t>382069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>738743</t>
+          <t>738713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>816587</t>
+          <t>809652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>195770</t>
+          <t>199473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>243158</t>
+          <t>248726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287727</t>
+          <t>289338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333606</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>497300</t>
+          <t>497854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>565080</t>
+          <t>561438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275989</t>
+          <t>270421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>323377</t>
+          <t>319674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182036</t>
+          <t>182981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227915</t>
+          <t>226304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>469709</t>
+          <t>473351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>537489</t>
+          <t>536935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237277</t>
+          <t>237421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>276383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266829</t>
+          <t>264720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302710</t>
+          <t>302428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>511728</t>
+          <t>514854</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>564882</t>
+          <t>566782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112415</t>
+          <t>110327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149433</t>
+          <t>149289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137157</t>
+          <t>139266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225814</t>
+          <t>223914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278968</t>
+          <t>275842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210136</t>
+          <t>210359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238977</t>
+          <t>239148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287974</t>
+          <t>287072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>310510</t>
+          <t>311285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>506641</t>
+          <t>504214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>545005</t>
+          <t>544802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53606</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82447</t>
+          <t>82224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32424</t>
+          <t>31649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54960</t>
+          <t>55862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90512</t>
+          <t>90715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128876</t>
+          <t>131303</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180769</t>
+          <t>180988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197639</t>
+          <t>197923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310899</t>
+          <t>311806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>326742</t>
+          <t>326613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497192</t>
+          <t>496791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521328</t>
+          <t>520188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46599</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1342788</t>
+          <t>1334686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1458215</t>
+          <t>1458948</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1870650</t>
+          <t>1865497</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1988583</t>
+          <t>1982855</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3234788</t>
+          <t>3242413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3405160</t>
+          <t>3406066</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1818328</t>
+          <t>1817595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1933755</t>
+          <t>1941857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1390614</t>
+          <t>1396342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1508547</t>
+          <t>1513700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3250581</t>
+          <t>3249675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3420953</t>
+          <t>3413328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91419</t>
+          <t>94077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129735</t>
+          <t>131573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103451</t>
+          <t>103348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140644</t>
+          <t>140516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207641</t>
+          <t>207106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257051</t>
+          <t>260054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324411</t>
+          <t>322573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362727</t>
+          <t>360069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289586</t>
+          <t>289714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326779</t>
+          <t>326882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627325</t>
+          <t>624322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>676735</t>
+          <t>677270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167111</t>
+          <t>167551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216336</t>
+          <t>218839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189943</t>
+          <t>189886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239787</t>
+          <t>237531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373800</t>
+          <t>370970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442490</t>
+          <t>443208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470751</t>
+          <t>468248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>519976</t>
+          <t>519536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370468</t>
+          <t>372724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>420312</t>
+          <t>420369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>854852</t>
+          <t>854134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>923542</t>
+          <t>926372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217299</t>
+          <t>219820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268944</t>
+          <t>269913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287134</t>
+          <t>290517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342443</t>
+          <t>343678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>523805</t>
+          <t>523238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603625</t>
+          <t>602145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>411950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464564</t>
+          <t>462043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>368407</t>
+          <t>367172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>423716</t>
+          <t>420333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789087</t>
+          <t>790567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>868907</t>
+          <t>869474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230001</t>
+          <t>230124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279067</t>
+          <t>280198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283072</t>
+          <t>282596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336471</t>
+          <t>333501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526603</t>
+          <t>525831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600686</t>
+          <t>601377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335550</t>
+          <t>334419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>384616</t>
+          <t>384493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279728</t>
+          <t>282698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333127</t>
+          <t>333603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630130</t>
+          <t>629439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>704213</t>
+          <t>704985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>232247</t>
+          <t>232439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>276063</t>
+          <t>275822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294446</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334479</t>
+          <t>335405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>537831</t>
+          <t>538259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597510</t>
+          <t>598497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153366</t>
+          <t>153607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197182</t>
+          <t>196990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113321</t>
+          <t>112395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153354</t>
+          <t>151766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279719</t>
+          <t>278732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339398</t>
+          <t>338970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>219790</t>
+          <t>220009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>251379</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>271407</t>
+          <t>272312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>301392</t>
+          <t>302640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>496940</t>
+          <t>497604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>542230</t>
+          <t>543145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>58398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89996</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52604</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>81684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121552</t>
+          <t>120637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166842</t>
+          <t>166178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>207648</t>
+          <t>204872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>228312</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>355666</t>
+          <t>356498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>374826</t>
+          <t>375849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>569236</t>
+          <t>569458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>598599</t>
+          <t>599113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>44979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>32481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69594</t>
+          <t>69372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1445255</t>
+          <t>1454404</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1572564</t>
+          <t>1573064</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1871924</t>
+          <t>1874277</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2000271</t>
+          <t>1994639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3353430</t>
+          <t>3351809</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3524304</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1854215</t>
+          <t>1853715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1981524</t>
+          <t>1972375</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1558038</t>
+          <t>1563670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1686385</t>
+          <t>1684032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3460784</t>
+          <t>3459693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3631658</t>
+          <t>3633279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60770</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96128</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>69523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104620</t>
+          <t>101529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140368</t>
+          <t>138144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185783</t>
+          <t>185355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323335</t>
+          <t>324554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358693</t>
+          <t>357587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291135</t>
+          <t>294226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324172</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629435</t>
+          <t>629863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674850</t>
+          <t>677074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109942</t>
+          <t>109295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149148</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111686</t>
+          <t>112602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151148</t>
+          <t>152634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232960</t>
+          <t>233131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294712</t>
+          <t>288277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441348</t>
+          <t>439772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480554</t>
+          <t>481201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412396</t>
+          <t>410910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451858</t>
+          <t>450942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>859328</t>
+          <t>865763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921080</t>
+          <t>920909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140417</t>
+          <t>138575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185994</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203313</t>
+          <t>200820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250847</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356612</t>
+          <t>350704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418472</t>
+          <t>419798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483103</t>
+          <t>485145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528680</t>
+          <t>530522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410539</t>
+          <t>410743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458073</t>
+          <t>460566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>912011</t>
+          <t>910685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>973871</t>
+          <t>979779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220343</t>
+          <t>223100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>272810</t>
+          <t>273604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>258166</t>
+          <t>256359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308973</t>
+          <t>311761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>496688</t>
+          <t>496219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568980</t>
+          <t>571859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>373238</t>
+          <t>372444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>425705</t>
+          <t>422948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340104</t>
+          <t>337316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>390911</t>
+          <t>392718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726145</t>
+          <t>723266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>798437</t>
+          <t>798906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>245864</t>
+          <t>247294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292461</t>
+          <t>293015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288959</t>
+          <t>289655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334322</t>
+          <t>334421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>546885</t>
+          <t>548012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>612163</t>
+          <t>614620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185457</t>
+          <t>184903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232054</t>
+          <t>230624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162527</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207890</t>
+          <t>207194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362604</t>
+          <t>360147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427882</t>
+          <t>426755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212003</t>
+          <t>210940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>245546</t>
+          <t>246079</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>272893</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>307998</t>
+          <t>307197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>494526</t>
+          <t>493320</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>542136</t>
+          <t>543729</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88784</t>
+          <t>88251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122327</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69764</t>
+          <t>70565</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104869</t>
+          <t>104297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169956</t>
+          <t>168363</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>217566</t>
+          <t>218772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199078</t>
+          <t>198488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220548</t>
+          <t>220966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>350242</t>
+          <t>349335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>375198</t>
+          <t>375838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>556053</t>
+          <t>558152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>590549</t>
+          <t>592086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>58510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49927</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66618</t>
+          <t>65081</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101114</t>
+          <t>99015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1270293</t>
+          <t>1265887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1381491</t>
+          <t>1383208</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1629512</t>
+          <t>1638475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1758713</t>
+          <t>1758059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2930007</t>
+          <t>2927561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3097352</t>
+          <t>3102177</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2012859</t>
+          <t>2011142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2124057</t>
+          <t>2128463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1785829</t>
+          <t>1786483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1915030</t>
+          <t>1906067</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3841540</t>
+          <t>3836715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4008885</t>
+          <t>4011331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53991</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108755</t>
+          <t>107285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>78722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102888</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171172</t>
+          <t>172524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291232</t>
+          <t>292702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345996</t>
+          <t>347133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232828</t>
+          <t>232895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271901</t>
+          <t>272803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540432</t>
+          <t>539080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608716</t>
+          <t>608634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105533</t>
+          <t>105211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155689</t>
+          <t>154688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77541</t>
+          <t>78466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162305</t>
+          <t>161511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197668</t>
+          <t>202569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300993</t>
+          <t>300776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267858</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318014</t>
+          <t>318336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348659</t>
+          <t>349453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433423</t>
+          <t>432498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633518</t>
+          <t>633735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736843</t>
+          <t>731942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159607</t>
+          <t>161319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206676</t>
+          <t>206187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180475</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219479</t>
+          <t>217927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352947</t>
+          <t>352429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>411689</t>
+          <t>411884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328693</t>
+          <t>329182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>375762</t>
+          <t>374050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322279</t>
+          <t>323831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361283</t>
+          <t>359398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665439</t>
+          <t>665244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>724181</t>
+          <t>724699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401311</t>
+          <t>402082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>737282</t>
+          <t>740869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310003</t>
+          <t>310617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>389298</t>
+          <t>389773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>761394</t>
+          <t>769556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1164682</t>
+          <t>1182120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148409</t>
+          <t>144822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>484380</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320014</t>
+          <t>319539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399309</t>
+          <t>398695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430321</t>
+          <t>412883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>833609</t>
+          <t>825447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304733</t>
+          <t>306794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>347126</t>
+          <t>347854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>332046</t>
+          <t>331223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366323</t>
+          <t>364648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>648415</t>
+          <t>646974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>705940</t>
+          <t>700569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207811</t>
+          <t>207083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>250204</t>
+          <t>248143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>180953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213555</t>
+          <t>214378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394598</t>
+          <t>399969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>452123</t>
+          <t>453564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214430</t>
+          <t>214867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244083</t>
+          <t>245406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>455492</t>
+          <t>458055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>566574</t>
+          <t>568026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>673993</t>
+          <t>672680</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>845734</t>
+          <t>851809</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>118355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149331</t>
+          <t>148894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151151</t>
+          <t>148588</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124671</t>
+          <t>118596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296412</t>
+          <t>297725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214828</t>
+          <t>216586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236328</t>
+          <t>235363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374806</t>
+          <t>374792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390872</t>
+          <t>390626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595903</t>
+          <t>595871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>622376</t>
+          <t>621752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>45055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>63832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75750</t>
+          <t>76374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102223</t>
+          <t>102255</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1557120</t>
+          <t>1563703</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2116180</t>
+          <t>2095632</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1855580</t>
+          <t>1855890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2301535</t>
+          <t>2301980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3473685</t>
+          <t>3474211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4140835</t>
+          <t>4180808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1327531</t>
+          <t>1348079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1886591</t>
+          <t>1880008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1342068</t>
+          <t>1341623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1788023</t>
+          <t>1787713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2946479</t>
+          <t>2906506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3613629</t>
+          <t>3613103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91246</t>
+          <t>90983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>129783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115759</t>
+          <t>113741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151828</t>
+          <t>150316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211240</t>
+          <t>214306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270100</t>
+          <t>271727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364636</t>
+          <t>364281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402818</t>
+          <t>403081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315661</t>
+          <t>317173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351730</t>
+          <t>353748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691453</t>
+          <t>689826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750313</t>
+          <t>747247</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152162</t>
+          <t>152199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200650</t>
+          <t>199549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221239</t>
+          <t>221084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270853</t>
+          <t>272529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>388090</t>
+          <t>386711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>456999</t>
+          <t>456927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>534839</t>
+          <t>535940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583327</t>
+          <t>583290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354641</t>
+          <t>352965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404255</t>
+          <t>404410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903983</t>
+          <t>904055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972892</t>
+          <t>974271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193646</t>
+          <t>194201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240804</t>
+          <t>243081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307675</t>
+          <t>307656</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>360907</t>
+          <t>360412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518760</t>
+          <t>515333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589699</t>
+          <t>586968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397864</t>
+          <t>395587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>445022</t>
+          <t>444467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328837</t>
+          <t>329332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382069</t>
+          <t>382088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>738713</t>
+          <t>741444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>809652</t>
+          <t>813079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199473</t>
+          <t>197942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248726</t>
+          <t>242984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289338</t>
+          <t>288014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332661</t>
+          <t>331631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>497854</t>
+          <t>498861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>561438</t>
+          <t>564547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270421</t>
+          <t>276163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319674</t>
+          <t>321205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182981</t>
+          <t>184011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226304</t>
+          <t>227628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473351</t>
+          <t>470242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536935</t>
+          <t>535928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237421</t>
+          <t>236645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>276383</t>
+          <t>273514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>70,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>284516</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>265334</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>300703</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>70,43%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>65,68%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>74,43%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>540547</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>513704</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>565116</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>71,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>284516</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>264720</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>302428</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>70,43%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>540547</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>514854</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>566782</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>113196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149289</t>
+          <t>150065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>119470</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>103283</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>138652</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>29,57%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>250149</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>225580</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>276992</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>28,53%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>119470</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101558</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139266</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>250149</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>223914</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>275842</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>28,32%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210359</t>
+          <t>210337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>239148</t>
+          <t>239085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287072</t>
+          <t>288851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>311285</t>
+          <t>311763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>504214</t>
+          <t>505358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>544802</t>
+          <t>543164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82224</t>
+          <t>82246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131303</t>
+          <t>130159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180988</t>
+          <t>179221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197923</t>
+          <t>197933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>311806</t>
+          <t>311919</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>326613</t>
+          <t>326993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>496791</t>
+          <t>498235</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520188</t>
+          <t>520733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1334686</t>
+          <t>1334087</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1458948</t>
+          <t>1455877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1865497</t>
+          <t>1867507</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1982855</t>
+          <t>1984856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3242413</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3406066</t>
+          <t>3411872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1820666</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1941857</t>
+          <t>1942456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1396342</t>
+          <t>1394341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1513700</t>
+          <t>1511690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3249675</t>
+          <t>3243869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3413328</t>
+          <t>3413200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>91935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131573</t>
+          <t>129238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103348</t>
+          <t>103882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140516</t>
+          <t>140733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207106</t>
+          <t>207263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260054</t>
+          <t>257606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322573</t>
+          <t>324908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360069</t>
+          <t>362211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289714</t>
+          <t>289497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326882</t>
+          <t>326348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>624322</t>
+          <t>626770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>677270</t>
+          <t>677113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167551</t>
+          <t>168308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218839</t>
+          <t>216574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189886</t>
+          <t>189795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237531</t>
+          <t>236382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370970</t>
+          <t>375604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443208</t>
+          <t>443049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468248</t>
+          <t>470513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>519536</t>
+          <t>518779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372724</t>
+          <t>373873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>420369</t>
+          <t>420460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>854134</t>
+          <t>854293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926372</t>
+          <t>921738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219820</t>
+          <t>222395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>271169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>290517</t>
+          <t>288485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>343678</t>
+          <t>343075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>523238</t>
+          <t>522043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>602145</t>
+          <t>599996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411950</t>
+          <t>410694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462043</t>
+          <t>459468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367172</t>
+          <t>367775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420333</t>
+          <t>422365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790567</t>
+          <t>792716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>869474</t>
+          <t>870669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230124</t>
+          <t>228057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280198</t>
+          <t>279399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>282596</t>
+          <t>284523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333501</t>
+          <t>338178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>525831</t>
+          <t>526007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601377</t>
+          <t>602877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334419</t>
+          <t>335218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>384493</t>
+          <t>386560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282698</t>
+          <t>278021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>331676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>629439</t>
+          <t>627939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>704985</t>
+          <t>704809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>232439</t>
+          <t>232410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>275822</t>
+          <t>272982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296034</t>
+          <t>297135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335405</t>
+          <t>337004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>538259</t>
+          <t>542198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>598497</t>
+          <t>602037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153607</t>
+          <t>156447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196990</t>
+          <t>197019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112395</t>
+          <t>110796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151766</t>
+          <t>150665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278732</t>
+          <t>275192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338970</t>
+          <t>335031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>220009</t>
+          <t>219302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>249746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>272312</t>
+          <t>271129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302640</t>
+          <t>301050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>497604</t>
+          <t>499261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>543145</t>
+          <t>544512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58398</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51356</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81684</t>
+          <t>82867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120637</t>
+          <t>119270</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166178</t>
+          <t>164521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204872</t>
+          <t>207171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228312</t>
+          <t>228810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>356498</t>
+          <t>356542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>375849</t>
+          <t>375958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>569458</t>
+          <t>568767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>599113</t>
+          <t>598872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69372</t>
+          <t>70063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1454404</t>
+          <t>1445018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1573064</t>
+          <t>1567650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1874277</t>
+          <t>1876130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1994639</t>
+          <t>1990743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3351809</t>
+          <t>3363111</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3526124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1853715</t>
+          <t>1859129</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1972375</t>
+          <t>1981761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1563670</t>
+          <t>1567566</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1684032</t>
+          <t>1682179</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3459693</t>
+          <t>3458964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3633279</t>
+          <t>3621977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>61277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94909</t>
+          <t>93775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>69089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138144</t>
+          <t>138434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185355</t>
+          <t>186808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324554</t>
+          <t>325688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357587</t>
+          <t>358186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294226</t>
+          <t>295215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326232</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629863</t>
+          <t>628410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>677074</t>
+          <t>676784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109295</t>
+          <t>109301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150724</t>
+          <t>150401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112602</t>
+          <t>111478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152634</t>
+          <t>150780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233131</t>
+          <t>232004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288277</t>
+          <t>290724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439772</t>
+          <t>440095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481201</t>
+          <t>481195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410910</t>
+          <t>412764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450942</t>
+          <t>452066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>865763</t>
+          <t>863316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920909</t>
+          <t>922036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138575</t>
+          <t>137802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183952</t>
+          <t>180280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200820</t>
+          <t>203204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250643</t>
+          <t>250168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350704</t>
+          <t>355516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419798</t>
+          <t>428876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485145</t>
+          <t>488817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530522</t>
+          <t>531295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410743</t>
+          <t>411218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>460566</t>
+          <t>458182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>910685</t>
+          <t>901607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>979779</t>
+          <t>974967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223100</t>
+          <t>221938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273604</t>
+          <t>274694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>256359</t>
+          <t>257327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311761</t>
+          <t>307640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>496219</t>
+          <t>498464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>571859</t>
+          <t>568049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>372444</t>
+          <t>371354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422948</t>
+          <t>424110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337316</t>
+          <t>341437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392718</t>
+          <t>391750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723266</t>
+          <t>727076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>798906</t>
+          <t>796661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247294</t>
+          <t>244890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>293015</t>
+          <t>291530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289655</t>
+          <t>288267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334421</t>
+          <t>334053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>548012</t>
+          <t>549372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614620</t>
+          <t>612684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184903</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230624</t>
+          <t>233028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>162796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207194</t>
+          <t>208582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360147</t>
+          <t>362083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426755</t>
+          <t>425395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210940</t>
+          <t>211373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>246079</t>
+          <t>245027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>273465</t>
+          <t>273452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>307197</t>
+          <t>308052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>493320</t>
+          <t>495776</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>543729</t>
+          <t>544901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88251</t>
+          <t>89303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123390</t>
+          <t>122957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70565</t>
+          <t>69710</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104297</t>
+          <t>104310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168363</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218772</t>
+          <t>216316</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198488</t>
+          <t>199865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220966</t>
+          <t>221934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>349335</t>
+          <t>349907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>375838</t>
+          <t>375707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>558152</t>
+          <t>557014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>592086</t>
+          <t>591236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58510</t>
+          <t>57133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99015</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1265887</t>
+          <t>1270190</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1383208</t>
+          <t>1384774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1638475</t>
+          <t>1632684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1758059</t>
+          <t>1752258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2927561</t>
+          <t>2928023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3102177</t>
+          <t>3099135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2011142</t>
+          <t>2009576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2128463</t>
+          <t>2124160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1786483</t>
+          <t>1792284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1906067</t>
+          <t>1911858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3836715</t>
+          <t>3839757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4011331</t>
+          <t>4010869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76970</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107285</t>
+          <t>110649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>70907</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78722</t>
+          <t>93330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>133929</t>
+          <t>153352</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>122875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172524</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>323017</t>
+          <t>325348</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292702</t>
+          <t>297144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347133</t>
+          <t>349836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>254658</t>
+          <t>290108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232895</t>
+          <t>267685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272803</t>
+          <t>309829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>577675</t>
+          <t>615457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539080</t>
+          <t>579777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608634</t>
+          <t>645934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>143263</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105211</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154688</t>
+          <t>171551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>131816</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78466</t>
+          <t>124593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161511</t>
+          <t>168557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>260812</t>
+          <t>288645</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202569</t>
+          <t>255506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>324285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>294551</t>
+          <t>333627</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268859</t>
+          <t>305339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318336</t>
+          <t>359574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>379148</t>
+          <t>355122</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349453</t>
+          <t>331947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432498</t>
+          <t>375911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>673699</t>
+          <t>688749</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633735</t>
+          <t>653109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731942</t>
+          <t>721888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>181722</t>
+          <t>204853</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161319</t>
+          <t>181363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206187</t>
+          <t>230131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>199190</t>
+          <t>228902</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182360</t>
+          <t>209765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217927</t>
+          <t>250230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>380913</t>
+          <t>433754</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352429</t>
+          <t>401455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>411884</t>
+          <t>467553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>353647</t>
+          <t>414996</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>329182</t>
+          <t>389718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374050</t>
+          <t>438486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>342568</t>
+          <t>392456</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323831</t>
+          <t>371128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359398</t>
+          <t>411593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>696215</t>
+          <t>807453</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665244</t>
+          <t>773654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>724699</t>
+          <t>839752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>545481</t>
+          <t>326974</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>402082</t>
+          <t>300902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>740869</t>
+          <t>354157</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>362355</t>
+          <t>383976</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310617</t>
+          <t>363133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>389773</t>
+          <t>403537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>907837</t>
+          <t>710950</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>769556</t>
+          <t>674435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1182120</t>
+          <t>745698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>340210</t>
+          <t>371605</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144822</t>
+          <t>344422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483609</t>
+          <t>397677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>346957</t>
+          <t>349220</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319539</t>
+          <t>329659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>398695</t>
+          <t>370063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>687166</t>
+          <t>720825</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412883</t>
+          <t>686077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>825447</t>
+          <t>757340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>344008</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>306794</t>
+          <t>319929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>347854</t>
+          <t>369094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>348357</t>
+          <t>387508</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331223</t>
+          <t>369424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364648</t>
+          <t>404190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>674658</t>
+          <t>731516</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>646974</t>
+          <t>700463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>700569</t>
+          <t>761326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>228636</t>
+          <t>258282</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207083</t>
+          <t>233196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>248143</t>
+          <t>282361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197244</t>
+          <t>218977</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180953</t>
+          <t>202295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214378</t>
+          <t>237061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>425880</t>
+          <t>477259</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399969</t>
+          <t>447449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>453564</t>
+          <t>508312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>229411</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214867</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>245406</t>
+          <t>266038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>511562</t>
+          <t>332668</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>458055</t>
+          <t>319754</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>568026</t>
+          <t>344267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>740974</t>
+          <t>583291</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>672680</t>
+          <t>562726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>851809</t>
+          <t>605835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>134350</t>
+          <t>151470</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118355</t>
+          <t>136054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148894</t>
+          <t>167725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>95081</t>
+          <t>104582</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148588</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>229431</t>
+          <t>256051</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118596</t>
+          <t>233507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297725</t>
+          <t>276616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>226029</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>216586</t>
+          <t>234823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235363</t>
+          <t>258034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>383552</t>
+          <t>417633</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374792</t>
+          <t>407712</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390626</t>
+          <t>425570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>609581</t>
+          <t>664025</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595871</t>
+          <t>648505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>621752</t>
+          <t>678371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>49575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63832</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>88545</t>
+          <t>99403</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76374</t>
+          <t>85057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102255</t>
+          <t>114923</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1563703</t>
+          <t>1537537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2095632</t>
+          <t>1660921</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1855890</t>
+          <t>1917711</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2301980</t>
+          <t>2026014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3474211</t>
+          <t>3480317</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4180808</t>
+          <t>3649031</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1728800</t>
+          <t>1916546</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1348079</t>
+          <t>1854182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1880008</t>
+          <t>1977566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1649811</t>
+          <t>1748651</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1341623</t>
+          <t>1689613</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1787713</t>
+          <t>1797916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3378611</t>
+          <t>3665197</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2906506</t>
+          <t>3581699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3613103</t>
+          <t>3750413</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
